--- a/FORM PERMINTAAN TENAGA KERJA IT.xlsx
+++ b/FORM PERMINTAAN TENAGA KERJA IT.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lw\staff baru\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1E2D60-4660-4EE1-8440-0DE2C0F1FB34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FORM" sheetId="2" r:id="rId1"/>
@@ -13,24 +19,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">FORM!$A$1:$M$20</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="57">
   <si>
     <t>PT. LEUWIJAYA UTAMA TEXTILE</t>
   </si>
@@ -313,14 +306,29 @@
   <si>
     <t>LEADER IT</t>
   </si>
+  <si>
+    <t>Karyawan atas nama Muhammad Jalliya, rencana resign tgl 16 Maret 2026</t>
+  </si>
+  <si>
+    <t>S1 - Teknik informatika</t>
+  </si>
+  <si>
+    <t>Minimal 1 tahun</t>
+  </si>
+  <si>
+    <t>tidak mengalami cacat fisik</t>
+  </si>
+  <si>
+    <t>mampu bekerja dalam tekanan, dapat management waktu dan prioritas, diharapkan IQ diatas 105</t>
+  </si>
+  <si>
+    <t>Memelihara aplikasi existing, membuat dan mengembangkan aplikasi baru, membuat report-report dan form SAP, menjaga ketersediaan program, mencari dan memperbaiki bug dalam program</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd\-mmm\-yy"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="12">
     <font>
       <sz val="11"/>
@@ -1122,7 +1130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1138,11 +1146,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1182,6 +1188,201 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="15" fontId="11" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="11" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1197,24 +1398,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1233,7 +1425,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1265,195 +1457,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1464,6 +1467,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1493,11 +1499,14 @@
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s2049"/>
                 </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001080000}"/>
+                </a:ext>
               </a:extLst>
             </xdr:cNvPr>
             <xdr:cNvSpPr/>
           </xdr:nvSpPr>
-          <xdr:spPr>
+          <xdr:spPr bwMode="auto">
             <a:xfrm>
               <a:off x="0" y="0"/>
               <a:ext cx="0" cy="0"/>
@@ -1505,6 +1514,16 @@
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
+            <a:noFill/>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
         </xdr:sp>
         <xdr:clientData/>
@@ -1527,7 +1546,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Flowchart: Process 2"/>
+        <xdr:cNvPr id="3" name="Flowchart: Process 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1677,7 +1702,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Flowchart: Process 3"/>
+        <xdr:cNvPr id="4" name="Flowchart: Process 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1827,7 +1858,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Flowchart: Process 4"/>
+        <xdr:cNvPr id="5" name="Flowchart: Process 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2222,7 +2259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M20"/>
   <sheetFormatPr defaultColWidth="24.140625" defaultRowHeight="14.25"/>
   <cols>
@@ -2243,87 +2280,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32.25" customHeight="1">
-      <c r="A1" s="83"/>
-      <c r="B1" s="84"/>
-      <c r="C1" s="93" t="s">
+      <c r="A1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="73" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="74"/>
+      <c r="M1" s="52"/>
     </row>
     <row r="2" spans="1:13" ht="33.75" customHeight="1">
-      <c r="A2" s="85"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="75" t="s">
+      <c r="A2" s="32"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="78" t="s">
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="79"/>
+      <c r="M2" s="57"/>
     </row>
     <row r="3" spans="1:13" ht="15.75">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="54"/>
-      <c r="E3" s="70" t="s">
+      <c r="D3" s="59"/>
+      <c r="E3" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54" t="s">
+      <c r="F3" s="59"/>
+      <c r="G3" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="51" t="s">
+      <c r="H3" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="80" t="s">
+      <c r="I3" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="51" t="s">
+      <c r="J3" s="61"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="62"/>
+      <c r="M3" s="64" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="32.25" thickBot="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="55"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="67"/>
       <c r="E4" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="55"/>
-      <c r="H4" s="52"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="65"/>
       <c r="I4" s="5" t="s">
         <v>14</v>
       </c>
@@ -2333,56 +2370,70 @@
       <c r="K4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M4" s="52"/>
+      <c r="M4" s="65"/>
     </row>
     <row r="5" spans="1:13" s="1" customFormat="1" ht="408.75" customHeight="1">
-      <c r="A5" s="107">
+      <c r="A5" s="48">
         <v>1</v>
       </c>
-      <c r="B5" s="105" t="s">
+      <c r="B5" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="101" t="s">
+      <c r="C5" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="102"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="99" t="s">
+      <c r="D5" s="45"/>
+      <c r="E5" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="42"/>
+      <c r="G5" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="H5" s="97"/>
-      <c r="I5" s="99"/>
-      <c r="J5" s="105"/>
-      <c r="K5" s="112"/>
-      <c r="L5" s="97"/>
-      <c r="M5" s="110"/>
+      <c r="H5" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="L5" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="M5" s="21">
+        <v>46119</v>
+      </c>
     </row>
     <row r="6" spans="1:13" s="1" customFormat="1">
-      <c r="A6" s="108"/>
-      <c r="B6" s="106"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="100"/>
-      <c r="F6" s="96"/>
-      <c r="G6" s="100"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="100"/>
-      <c r="J6" s="106"/>
-      <c r="K6" s="113"/>
-      <c r="L6" s="98"/>
-      <c r="M6" s="111"/>
+      <c r="A6" s="49"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="22"/>
     </row>
     <row r="7" spans="1:13" ht="24" customHeight="1">
-      <c r="A7" s="109" t="s">
+      <c r="A7" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="109"/>
-      <c r="C7" s="109"/>
-      <c r="D7" s="109"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
       <c r="E7" s="6" t="s">
         <v>19</v>
       </c>
@@ -2392,275 +2443,262 @@
       <c r="G7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="M7" s="20"/>
+      <c r="M7" s="18"/>
     </row>
     <row r="8" spans="1:13" ht="24" customHeight="1" thickBot="1">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="M8" s="21"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="M8" s="19"/>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1" thickBot="1">
-      <c r="F9" s="45" t="s">
+      <c r="F9" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="47"/>
-      <c r="H9" s="18" t="s">
+      <c r="G9" s="107"/>
+      <c r="H9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="45" t="s">
+      <c r="I9" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="46"/>
-      <c r="K9" s="47"/>
-      <c r="L9" s="23" t="s">
+      <c r="J9" s="106"/>
+      <c r="K9" s="107"/>
+      <c r="L9" s="86" t="s">
         <v>25</v>
       </c>
-      <c r="M9" s="24"/>
+      <c r="M9" s="87"/>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="10" t="s">
+      <c r="B10" s="89"/>
+      <c r="C10" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="48"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="56"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="90"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="108"/>
+      <c r="I10" s="96"/>
+      <c r="J10" s="97"/>
+      <c r="K10" s="98"/>
+      <c r="L10" s="85"/>
+      <c r="M10" s="68"/>
     </row>
     <row r="11" spans="1:13" ht="24" customHeight="1">
-      <c r="A11" s="87" t="s">
+      <c r="A11" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="88"/>
-      <c r="C11" s="11" t="s">
+      <c r="B11" s="35"/>
+      <c r="C11" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="89"/>
-      <c r="E11" s="89"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="53"/>
-      <c r="M11" s="56"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="109"/>
+      <c r="I11" s="99"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="101"/>
+      <c r="L11" s="66"/>
+      <c r="M11" s="68"/>
     </row>
     <row r="12" spans="1:13" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A12" s="90" t="s">
+      <c r="A12" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="91"/>
-      <c r="C12" s="12" t="s">
+      <c r="B12" s="38"/>
+      <c r="C12" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="92"/>
-      <c r="E12" s="92"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="56"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="110"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="103"/>
+      <c r="K12" s="104"/>
+      <c r="L12" s="66"/>
+      <c r="M12" s="68"/>
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="58"/>
-      <c r="C13" s="63" t="s">
+      <c r="B13" s="70"/>
+      <c r="C13" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="17" t="s">
+      <c r="D13" s="76"/>
+      <c r="E13" s="76"/>
+      <c r="F13" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I13" s="29" t="s">
+      <c r="I13" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="J13" s="34"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="29" t="s">
+      <c r="J13" s="94"/>
+      <c r="K13" s="95"/>
+      <c r="L13" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="M13" s="30"/>
+      <c r="M13" s="92"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="59"/>
-      <c r="B14" s="60"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="17" t="s">
+      <c r="A14" s="71"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="78"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="I14" s="29" t="s">
+      <c r="I14" s="91" t="s">
         <v>40</v>
       </c>
-      <c r="J14" s="34"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="29" t="s">
+      <c r="J14" s="94"/>
+      <c r="K14" s="95"/>
+      <c r="L14" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="30"/>
+      <c r="M14" s="92"/>
     </row>
     <row r="15" spans="1:13" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A15" s="61"/>
-      <c r="B15" s="62"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="14" t="s">
+      <c r="A15" s="73"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="H15" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="I15" s="31" t="s">
+      <c r="I15" s="81" t="s">
         <v>31</v>
       </c>
-      <c r="J15" s="32"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="31" t="s">
+      <c r="J15" s="93"/>
+      <c r="K15" s="82"/>
+      <c r="L15" s="81" t="s">
         <v>31</v>
       </c>
-      <c r="M15" s="33"/>
+      <c r="M15" s="82"/>
     </row>
     <row r="16" spans="1:13" ht="15" customHeight="1">
-      <c r="A16" s="69" t="s">
+      <c r="A16" s="83" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="69"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="69"/>
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="83"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="63" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
-      <c r="M17" s="28"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="63"/>
+      <c r="L17" s="63"/>
+      <c r="M17" s="63"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="28"/>
-      <c r="M18" s="28"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="63"/>
+      <c r="K18" s="63"/>
+      <c r="L18" s="63"/>
+      <c r="M18" s="63"/>
     </row>
     <row r="19" spans="1:13">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="28"/>
+      <c r="B19" s="63"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="63"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="63"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
+      <c r="B20" s="63"/>
+      <c r="C20" s="63"/>
+      <c r="D20" s="63"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="63"/>
+      <c r="K20" s="63"/>
+      <c r="L20" s="63"/>
+      <c r="M20" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="C1:K1"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="C2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I10:K12"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H10:H12"/>
     <mergeCell ref="A19:M19"/>
     <mergeCell ref="A20:M20"/>
     <mergeCell ref="A3:A4"/>
@@ -2677,19 +2715,30 @@
     <mergeCell ref="C3:D4"/>
     <mergeCell ref="L10:M12"/>
     <mergeCell ref="A17:M17"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A18:M18"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I10:K12"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H10:H12"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="C5:D6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="I5:I6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.35433070866141736" top="0.27559055118110237" bottom="0.23622047244094491" header="0.11811023622047245" footer="0.31496062992125984"/>
